--- a/assets/files/Data-Penjualan-Multi-Dimensi.xlsx
+++ b/assets/files/Data-Penjualan-Multi-Dimensi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0EE5E89-7F2F-44B2-910B-9EAEFEABDBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918E76A4-0629-436A-AE5F-D69924D7DCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8FFB06A0-A562-4EE0-BDC1-E8DA07409666}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -375,22 +375,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -408,7 +408,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -417,42 +417,7 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -533,13 +498,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
@@ -552,6 +510,48 @@
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -635,7 +635,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -856,7 +856,63 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="&quot;Rp&quot;#,##0" sourceLinked="0"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Rp dalam Jutaan</a:t>
+                </a:r>
+                <a:endParaRPr lang="id-ID"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -890,6 +946,9 @@
         <c:crossAx val="1693556224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:dispUnits>
+          <c:builtInUnit val="millions"/>
+        </c:dispUnits>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1048,6 +1107,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1832-4944-A703-6C2AD14A0946}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1063,6 +1127,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1832-4944-A703-6C2AD14A0946}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -3221,15 +3290,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>138112</xdr:rowOff>
+      <xdr:colOff>230981</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>114301</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3257,15 +3326,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>153987</xdr:rowOff>
+      <xdr:colOff>235745</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>39687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
+      <xdr:colOff>581025</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>39687</xdr:rowOff>
+      <xdr:rowOff>115887</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3339,8 +3408,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>26458</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Region">
@@ -3363,7 +3432,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3417,8 +3486,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>26458</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Produk">
@@ -3441,7 +3510,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3513,13 +3582,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{15DDDABC-E7A6-4DFC-9DE7-C986FED034C8}" name="Table1" displayName="Table1" ref="A1:D13" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{15DDDABC-E7A6-4DFC-9DE7-C986FED034C8}" name="Table1" displayName="Table1" ref="A1:D13" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:D13" xr:uid="{15DDDABC-E7A6-4DFC-9DE7-C986FED034C8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1605F078-0206-487E-9112-7FB21E999E4B}" name="Bulan" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{20D68AEC-7607-4F1B-AC84-93A2E68D3012}" name="Region" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{F56E30B7-56E9-4502-927B-43DDF9692DB4}" name="Produk" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{B06F1E3E-02E5-4DBD-AAE8-CE6FAEAE5FD2}" name="Penjualan" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{1605F078-0206-487E-9112-7FB21E999E4B}" name="Bulan" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{20D68AEC-7607-4F1B-AC84-93A2E68D3012}" name="Region" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{F56E30B7-56E9-4502-927B-43DDF9692DB4}" name="Produk" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{B06F1E3E-02E5-4DBD-AAE8-CE6FAEAE5FD2}" name="Penjualan" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
